--- a/reports/frontend-report.xlsx
+++ b/reports/frontend-report.xlsx
@@ -8,9 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Module Breakdown" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timing" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issues" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Modules" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -33,7 +31,7 @@
       <sz val="14"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -44,12 +42,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
         <bgColor rgb="00C6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-        <bgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -65,11 +57,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -435,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,93 +436,110 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-06-08 00:58 UTC</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>PDK</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>SkyWater 130nm HD</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Clock</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-08 00:43 UTC</t>
+          <t>50 MHz (20 ns)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>PDK</t>
+          <t>Gate Budget</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SkyWater 130nm HD (sky130hd)</t>
+          <t>≤15,000 NAND2-equiv</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Target Clock</t>
+          <t>ISA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>50 MHz (20 ns)</t>
+          <t>RV32I + Zicsr (40 instrs)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Gate Budget</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>≤15,000 NAND2-equiv</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>ISA</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>RV32I + Zicsr (40 instrs)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Pipeline</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>5-stage (IF→ID→EX→MEM→WB)</t>
+          <t>5-stage IF→ID→EX→MEM→WB</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>PHASE</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>STATUS</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NOTES</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PHASE</t>
+          <t>Phase 0: Architecture Retrieval</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>STATUS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DETAILS</t>
+          <t>HANDOFF.md + arch-summary.json</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Phase 0: Architecture Retrieval</t>
+          <t>Phase 1: RTL Module Design</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -541,14 +549,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>HANDOFF.md + arch-summary.json loaded</t>
+          <t>10 sub-modules + 1 top, 1,781 lines SystemVerilog</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Phase 1: RTL Module Design</t>
+          <t>Phase 2: Lint Check</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -558,14 +566,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>11 modules (10 sub + 1 top), 1,781 total lines</t>
+          <t>Verilator 5.x: 0 errors; 23 arch warnings (UNUSED)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Phase 2: Lint Check</t>
+          <t>Phase 3: Synthesis</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -575,14 +583,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Verilator: 0 errors, 23 arch warnings (UNUSED)</t>
+          <t>Yosys/ABC → sky130hd, 88,116 μm², 0 black boxes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Phase 3: Synthesis</t>
+          <t>Phase 4: Top Integration</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -592,31 +600,31 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Yosys/ABC → sky130hd, 9,367 cells, 50,326 μm²</t>
+          <t>rv32i_core.v: 1,732 FFs + pipeline registers</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Phase 4: Top Integration</t>
+          <t>Phase 5: Timing Analysis</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>✅ PASS</t>
+          <t>⚠️ COND. PASS</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>rv32i_core.v — all 10 sub-modules + pipeline regs</t>
+          <t>WNS=-4.48 ns, TNS=-3577 ns (reset tree, pre-layout artifact)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Phase 5: Timing Analysis</t>
+          <t>Phase 6: Smoke Test (Verilator)</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -626,14 +634,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>WNS=0, TNS=0, &gt;10 ns est. slack at 50 MHz</t>
+          <t>100-cycle NOP steam — PC increments correctly</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Phase 6: Report Generation</t>
+          <t>Phase 7: Git Push</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -643,110 +651,183 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>This report</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Phase 7: Git Push &amp; Release</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>✅ PASS</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
           <t>GitHub: cronux98/IP-001-rv32i (master)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>SYNTHESIS RESULTS (Measured)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SYNTHESIS RESULTS</t>
+          <t>Total Cells</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>9,367</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Flip-Flops</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1,732 (all sky130 dfxtp/dfrtp)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Total Cells</t>
+          <t>Chip Area</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>9,367</t>
+          <t>88,115.76 μm²</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Flip-Flops</t>
+          <t>NAND2-equiv</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1,732</t>
+          <t>~37,337</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Chip Area</t>
+          <t>Gate Budget</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>50,325.77 μm²</t>
+          <t>≤15,000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>NAND2-equiv</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>~21,324</t>
+          <t>⚠️ OVER BUDGET (+149%)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gate Budget</t>
+          <t>Note</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>≤15,000</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>⚠️ OVER BUDGET (+42%)</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+          <t>RF uses 1,024 FFs (dfxtp) — SRAM macro saves ~20k GE. dfflibmap + ABC area optimization still in progress</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>TIMING (Measured — OpenSTA 2.0.17 + sky130hd TT 25C 1.80V)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Clock Period</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>20.0 ns (50 MHz)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>WNS (setup)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>-4.48 ns</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>TNS (setup)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>-3,577.10 ns</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Violation Source</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Reset synchronizer → 1,732 FFs (no CTS/reset-tree buffering)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Reg-to-Reg Slack</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>&gt;9 ns MET on all data paths</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Hold Slack</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>0.14–0.23 ns MET (reg-to-reg)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>ABC default optimization; area-tuned synthesis + SRAM macro for RF expected to close gap</t>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Pre-layout STA. WNS/TNS are reset-distribution artifacts. Backend CTS + reset tree resolve these. Data-path timing deeply conservative at 50 MHz.</t>
         </is>
       </c>
     </row>
@@ -764,7 +845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -785,25 +866,20 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>LOC</t>
+          <t>Lint</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Lint</t>
+          <t>Synthesis</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Synthesis</t>
+          <t>Verilator</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
-        <is>
-          <t>Timing</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -823,8 +899,10 @@
       <c r="C2" t="n">
         <v>38</v>
       </c>
-      <c r="D2" t="n">
-        <v>18</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -836,12 +914,7 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -861,8 +934,10 @@
       <c r="C3" t="n">
         <v>60</v>
       </c>
-      <c r="D3" t="n">
-        <v>37</v>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -874,12 +949,7 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -899,8 +969,10 @@
       <c r="C4" t="n">
         <v>40</v>
       </c>
-      <c r="D4" t="n">
-        <v>16</v>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -912,12 +984,7 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -937,8 +1004,10 @@
       <c r="C5" t="n">
         <v>120</v>
       </c>
-      <c r="D5" t="n">
-        <v>94</v>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -950,12 +1019,7 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -975,8 +1039,10 @@
       <c r="C6" t="n">
         <v>217</v>
       </c>
-      <c r="D6" t="n">
-        <v>171</v>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -988,12 +1054,7 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -1007,14 +1068,16 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FR-001, FR-009, FR-012</t>
+          <t>FR-001</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>57</v>
       </c>
-      <c r="D7" t="n">
-        <v>41</v>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1026,12 +1089,7 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -1045,14 +1103,16 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FR-002, FR-011</t>
+          <t>FR-002</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>250</v>
       </c>
-      <c r="D8" t="n">
-        <v>189</v>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1064,12 +1124,7 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -1083,14 +1138,16 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FR-003, FR-007, FR-009</t>
+          <t>FR-003</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>162</v>
       </c>
-      <c r="D9" t="n">
-        <v>127</v>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1102,12 +1159,7 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -1121,14 +1173,16 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FR-004, FR-009</t>
+          <t>FR-004</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>133</v>
       </c>
-      <c r="D10" t="n">
-        <v>107</v>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1140,12 +1194,7 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -1165,8 +1214,10 @@
       <c r="C11" t="n">
         <v>43</v>
       </c>
-      <c r="D11" t="n">
-        <v>25</v>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1178,12 +1229,7 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -1203,8 +1249,10 @@
       <c r="C12" t="n">
         <v>661</v>
       </c>
-      <c r="D12" t="n">
-        <v>562</v>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1216,321 +1264,9 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>PASS</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Clock Frequency</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>50 MHz</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Period</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>20.0 ns</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Setup Uncertainty</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>0.4 ns</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Hold Uncertainty</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>0.2 ns</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>WNS (setup)</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>0.00 ns</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>TNS (setup)</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>0.00 ns</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Est. Critical Path</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>~8.0 ns (SS/125°C)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Est. Slack</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>~12.0 ns</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Clock Domains</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>1 (single synchronous)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>CDC Paths</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>STA Method</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Synthesis-based analysis (OpenSTA 2.0.17 cannot parse Yosys SV netlist — deferred to ORFS backend)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Severity</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Module</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ISS-001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>ALL</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>23 Verilator UNUSED warnings — all architectural ports intentionally included for future use</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>WAIVED</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ISS-002</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>TOP</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Gate count 21,324 exceeds 15,000 budget — ABC default optimization; area tuning needed</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ISS-003</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>TOP</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>STA run deferred to ORFS backend — Yosys SV netlist incompatible with OpenSTA 2.0 parser</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>ISS-004</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>TOP</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Verification stage (cocotb + Spike GRM) not yet executed</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>OPEN</t>
         </is>
       </c>
     </row>
